--- a/01_Thermal/B_results/single_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_gp_analysis.xlsx
@@ -483,16 +483,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>19.93227206291802</v>
+        <v>5.316211201385351</v>
       </c>
       <c r="E2" t="n">
-        <v>25.48647331499784</v>
+        <v>1.059657280450655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4574212170103216</v>
+        <v>0.05611123567304827</v>
       </c>
       <c r="G2" t="n">
-        <v>2511.573847332075</v>
+        <v>37.7931427287662</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -511,16 +511,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>16.03720048545357</v>
+        <v>7.149121290940379</v>
       </c>
       <c r="E3" t="n">
-        <v>13.9452084414981</v>
+        <v>2.412375082713418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1373566017815918</v>
+        <v>0.06264973332930582</v>
       </c>
       <c r="G3" t="n">
-        <v>184.9552443677061</v>
+        <v>38.47742745768466</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -539,16 +539,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>15.96054128074436</v>
+        <v>6.947861024996403</v>
       </c>
       <c r="E4" t="n">
-        <v>17.46916584541142</v>
+        <v>2.008452435602874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3268042616335176</v>
+        <v>0.08172831157172519</v>
       </c>
       <c r="G4" t="n">
-        <v>970.9247904152544</v>
+        <v>60.72327988049094</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -567,16 +567,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>9.935691334394043</v>
+        <v>9.177508922901374</v>
       </c>
       <c r="E5" t="n">
-        <v>5.70103186360675</v>
+        <v>4.670545449111994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06534230898359385</v>
+        <v>0.05704789313606046</v>
       </c>
       <c r="G5" t="n">
-        <v>305.8787993476448</v>
+        <v>233.1522670704965</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -595,16 +595,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>11.58379565967958</v>
+        <v>10.15806109717185</v>
       </c>
       <c r="E6" t="n">
-        <v>5.166480146027773</v>
+        <v>5.993725396645205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.102848838829091</v>
+        <v>0.09796183476908378</v>
       </c>
       <c r="G6" t="n">
-        <v>169.73978431334</v>
+        <v>153.9921851038078</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -623,16 +623,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>8.140822201132078</v>
+        <v>6.723296833454137</v>
       </c>
       <c r="E7" t="n">
-        <v>3.054042498691909</v>
+        <v>2.149800356127943</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1180027175481368</v>
+        <v>0.08742295883459626</v>
       </c>
       <c r="G7" t="n">
-        <v>75.2495531803529</v>
+        <v>41.30198358019971</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -651,16 +651,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>9.678643412393903</v>
+        <v>6.451379003601372</v>
       </c>
       <c r="E8" t="n">
-        <v>2.589931866739402</v>
+        <v>0.9692166146484824</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06497669868203118</v>
+        <v>0.04744876434512554</v>
       </c>
       <c r="G8" t="n">
-        <v>82.43358210172131</v>
+        <v>43.95807870632481</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -677,16 +677,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>91.26896643671554</v>
+        <v>51.92343937445087</v>
       </c>
       <c r="E9" t="n">
-        <v>73.4123339769732</v>
+        <v>19.26377261530057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1731110873539931</v>
+        <v>0.06516331124277359</v>
       </c>
       <c r="G9" t="n">
-        <v>4300.755601058096</v>
+        <v>609.3983645277706</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/single_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_gp_analysis.xlsx
@@ -483,16 +483,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>5.316211201385351</v>
+        <v>4.053601106805763</v>
       </c>
       <c r="E2" t="n">
-        <v>1.059657280450655</v>
+        <v>0.6026532808311876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05611123567304827</v>
+        <v>0.03842740224161371</v>
       </c>
       <c r="G2" t="n">
-        <v>37.7931427287662</v>
+        <v>17.7253734881638</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -511,16 +511,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>7.149121290940379</v>
+        <v>5.322892412070852</v>
       </c>
       <c r="E3" t="n">
-        <v>2.412375082713418</v>
+        <v>1.507873959979012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06264973332930582</v>
+        <v>0.04501581218634044</v>
       </c>
       <c r="G3" t="n">
-        <v>38.47742745768466</v>
+        <v>19.86542016088185</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -539,16 +539,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>6.947861024996403</v>
+        <v>5.567049161436568</v>
       </c>
       <c r="E4" t="n">
-        <v>2.008452435602874</v>
+        <v>1.441635945114444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08172831157172519</v>
+        <v>0.06372834114267574</v>
       </c>
       <c r="G4" t="n">
-        <v>60.72327988049094</v>
+        <v>36.92116492278084</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -567,16 +567,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>9.177508922901374</v>
+        <v>7.304690174106151</v>
       </c>
       <c r="E5" t="n">
-        <v>4.670545449111994</v>
+        <v>3.897990138712019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05704789313606046</v>
+        <v>0.039186544618123</v>
       </c>
       <c r="G5" t="n">
-        <v>233.1522670704965</v>
+        <v>110.0105568490274</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -595,16 +595,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>10.15806109717185</v>
+        <v>8.727719200885645</v>
       </c>
       <c r="E6" t="n">
-        <v>5.993725396645205</v>
+        <v>5.167279917622548</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09796183476908378</v>
+        <v>0.08410877446406759</v>
       </c>
       <c r="G6" t="n">
-        <v>153.9921851038078</v>
+        <v>113.5187160156764</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -623,16 +623,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>6.723296833454137</v>
+        <v>5.359913581144015</v>
       </c>
       <c r="E7" t="n">
-        <v>2.149800356127943</v>
+        <v>1.42628317311139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08742295883459626</v>
+        <v>0.0672018369554928</v>
       </c>
       <c r="G7" t="n">
-        <v>41.30198358019971</v>
+        <v>24.40519020199147</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -651,16 +651,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>6.451379003601372</v>
+        <v>4.989071608789196</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9692166146484824</v>
+        <v>0.6675250911392508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04744876434512554</v>
+        <v>0.03594979591534166</v>
       </c>
       <c r="G8" t="n">
-        <v>43.95807870632481</v>
+        <v>25.23374713228151</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -677,16 +677,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>51.92343937445087</v>
+        <v>41.32493724523819</v>
       </c>
       <c r="E9" t="n">
-        <v>19.26377261530057</v>
+        <v>14.71124150650985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06516331124277359</v>
+        <v>0.04922009667550306</v>
       </c>
       <c r="G9" t="n">
-        <v>609.3983645277706</v>
+        <v>347.6801687708032</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/single_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_gp_analysis.xlsx
@@ -483,16 +483,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>4.053601106805763</v>
+        <v>18.85727389639767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6026532808311876</v>
+        <v>22.78763236663048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03842740224161371</v>
+        <v>0.4343216199199577</v>
       </c>
       <c r="G2" t="n">
-        <v>17.7253734881638</v>
+        <v>2264.311848078115</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -511,16 +511,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>5.322892412070852</v>
+        <v>15.25939619449679</v>
       </c>
       <c r="E3" t="n">
-        <v>1.507873959979012</v>
+        <v>12.38059159520043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04501581218634044</v>
+        <v>0.1322751662198958</v>
       </c>
       <c r="G3" t="n">
-        <v>19.86542016088185</v>
+        <v>171.523727660828</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -539,16 +539,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>5.567049161436568</v>
+        <v>15.85987035493103</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441635945114444</v>
+        <v>18.17714412333346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06372834114267574</v>
+        <v>0.3327705714836875</v>
       </c>
       <c r="G4" t="n">
-        <v>36.92116492278084</v>
+        <v>1006.699823800198</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -567,16 +567,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>7.304690174106151</v>
+        <v>9.880282797468041</v>
       </c>
       <c r="E5" t="n">
-        <v>3.897990138712019</v>
+        <v>5.67160341987807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.039186544618123</v>
+        <v>0.06497447137683202</v>
       </c>
       <c r="G5" t="n">
-        <v>110.0105568490274</v>
+        <v>302.4446680716975</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -595,16 +595,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>8.727719200885645</v>
+        <v>11.20182582496569</v>
       </c>
       <c r="E6" t="n">
-        <v>5.167279917622548</v>
+        <v>4.914608507028374</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08410877446406759</v>
+        <v>0.100018362759265</v>
       </c>
       <c r="G6" t="n">
-        <v>113.5187160156764</v>
+        <v>160.5256150429997</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -623,16 +623,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>5.359913581144015</v>
+        <v>7.642447493384552</v>
       </c>
       <c r="E7" t="n">
-        <v>1.42628317311139</v>
+        <v>2.598602577244985</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0672018369554928</v>
+        <v>0.1081373533909287</v>
       </c>
       <c r="G7" t="n">
-        <v>24.40519020199147</v>
+        <v>63.19335016763585</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -651,16 +651,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>4.989071608789196</v>
+        <v>7.755218956688658</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6675250911392508</v>
+        <v>1.547987992531003</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03594979591534166</v>
+        <v>0.05135420700183138</v>
       </c>
       <c r="G8" t="n">
-        <v>25.23374713228151</v>
+        <v>51.49214017420562</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -677,16 +677,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>41.32493724523819</v>
+        <v>86.45631551833245</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71124150650985</v>
+        <v>68.07817058184681</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04922009667550306</v>
+        <v>0.1673693214163189</v>
       </c>
       <c r="G9" t="n">
-        <v>347.6801687708032</v>
+        <v>4020.191172995679</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/single_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_gp_analysis.xlsx
@@ -483,19 +483,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>18.85727389639767</v>
+        <v>18.90749907987127</v>
       </c>
       <c r="E2" t="n">
-        <v>22.78763236663048</v>
+        <v>23.22911822391801</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4343216199199577</v>
+        <v>0.2180363384302348</v>
       </c>
       <c r="G2" t="n">
-        <v>2264.311848078115</v>
+        <v>1193.023838277972</v>
       </c>
       <c r="H2" t="n">
-        <v>12003.65050354092</v>
+        <v>25095.24045331192</v>
       </c>
     </row>
     <row r="3">
@@ -511,19 +511,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>15.25939619449679</v>
+        <v>15.57939975654868</v>
       </c>
       <c r="E3" t="n">
-        <v>12.38059159520043</v>
+        <v>12.53531602568521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1322751662198958</v>
+        <v>0.157104807222537</v>
       </c>
       <c r="G3" t="n">
-        <v>171.523727660828</v>
+        <v>170.2309164136433</v>
       </c>
       <c r="H3" t="n">
-        <v>9803.193489796933</v>
+        <v>6896.988293181215</v>
       </c>
     </row>
     <row r="4">
@@ -539,19 +539,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>15.85987035493103</v>
+        <v>15.45502942450964</v>
       </c>
       <c r="E4" t="n">
-        <v>18.17714412333346</v>
+        <v>17.69861305903508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3327705714836875</v>
+        <v>0.2858062448074364</v>
       </c>
       <c r="G4" t="n">
-        <v>1006.699823800198</v>
+        <v>957.488010612871</v>
       </c>
       <c r="H4" t="n">
-        <v>9090.968804657296</v>
+        <v>11721.6815093248</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>9.880282797468041</v>
+        <v>9.884016048348048</v>
       </c>
       <c r="E5" t="n">
-        <v>5.67160341987807</v>
+        <v>5.352186118546602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06497447137683202</v>
+        <v>0.06971758693784953</v>
       </c>
       <c r="G5" t="n">
-        <v>302.4446680716975</v>
+        <v>222.4914237698673</v>
       </c>
       <c r="H5" t="n">
-        <v>71640.79933933762</v>
+        <v>45775.02407050147</v>
       </c>
     </row>
     <row r="6">
@@ -595,19 +595,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>11.20182582496569</v>
+        <v>10.96621843454862</v>
       </c>
       <c r="E6" t="n">
-        <v>4.914608507028374</v>
+        <v>4.614124113547518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.100018362759265</v>
+        <v>0.1024701021812095</v>
       </c>
       <c r="G6" t="n">
-        <v>160.5256150429997</v>
+        <v>169.8980278739155</v>
       </c>
       <c r="H6" t="n">
-        <v>16046.66774128612</v>
+        <v>16180.57680150592</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +623,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>7.642447493384552</v>
+        <v>7.975669895822543</v>
       </c>
       <c r="E7" t="n">
-        <v>2.598602577244985</v>
+        <v>2.723576961368719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1081373533909287</v>
+        <v>0.06973702586808317</v>
       </c>
       <c r="G7" t="n">
-        <v>63.19335016763585</v>
+        <v>47.56686842690799</v>
       </c>
       <c r="H7" t="n">
-        <v>5404.056829595331</v>
+        <v>9780.875189666229</v>
       </c>
     </row>
     <row r="8">
@@ -651,19 +651,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>7.755218956688658</v>
+        <v>7.911426470323258</v>
       </c>
       <c r="E8" t="n">
-        <v>1.547987992531003</v>
+        <v>1.520527480321243</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05135420700183138</v>
+        <v>0.06772403359494376</v>
       </c>
       <c r="G8" t="n">
-        <v>51.49214017420562</v>
+        <v>39.0594114745147</v>
       </c>
       <c r="H8" t="n">
-        <v>19524.90314262348</v>
+        <v>8516.086466998437</v>
       </c>
     </row>
     <row r="9">
@@ -677,19 +677,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>86.45631551833245</v>
+        <v>86.67925910997207</v>
       </c>
       <c r="E9" t="n">
-        <v>68.07817058184681</v>
+        <v>67.67346198242238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1673693214163189</v>
+        <v>0.1502824143137006</v>
       </c>
       <c r="G9" t="n">
-        <v>4020.191172995679</v>
+        <v>2799.758496849691</v>
       </c>
       <c r="H9" t="n">
-        <v>143514.2398508377</v>
+        <v>123966.47278449</v>
       </c>
     </row>
   </sheetData>
